--- a/Master_dataset.xlsx
+++ b/Master_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52001527c413c64d/Dokumente/UT 25_26/Master_Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{2732C158-E860-47DA-9F96-065D957E2F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C829515-FE74-406A-9330-4621AD604396}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{2732C158-E860-47DA-9F96-065D957E2F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DF93A9E-3336-41E8-A02C-4064A9D5FC64}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B807EAFF-52F5-4185-96DB-AEC50A0340A8}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B807EAFF-52F5-4185-96DB-AEC50A0340A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -6755,34 +6755,34 @@
         <v>178</v>
       </c>
       <c r="C86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="300" x14ac:dyDescent="0.25">
@@ -22570,6 +22570,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a910aced-94ca-4ce0-b913-75b676fa2556" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B138497DA7A59F43BA2F46767FB6205D" ma:contentTypeVersion="5" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="4553f1f3e8e459fc3043270d2afcdea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a910aced-94ca-4ce0-b913-75b676fa2556" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="264701d59f9a0371d10288cfbf567d37" ns3:_="">
     <xsd:import namespace="a910aced-94ca-4ce0-b913-75b676fa2556"/>
@@ -22719,24 +22736,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08112C48-1B84-4823-AFFC-9219F8C86DBE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a910aced-94ca-4ce0-b913-75b676fa2556"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a910aced-94ca-4ce0-b913-75b676fa2556" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8779121B-A75C-4E89-9F89-BD5405D39DEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96BDB233-78B1-4C88-8721-0EE7AA90860B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22752,28 +22776,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8779121B-A75C-4E89-9F89-BD5405D39DEC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08112C48-1B84-4823-AFFC-9219F8C86DBE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a910aced-94ca-4ce0-b913-75b676fa2556"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>